--- a/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>DRTS</t>
   </si>
@@ -656,86 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -784,8 +791,14 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,8 +847,14 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,8 +903,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,44 +929,46 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F12" s="3">
         <v>6000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>6300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>4800</v>
       </c>
       <c r="H12" s="3">
         <v>5400</v>
       </c>
       <c r="I12" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>11400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>3000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -954,8 +981,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,8 +1037,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1037,14 +1076,14 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1093,14 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1149,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,58 +1172,66 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F17" s="3">
         <v>8200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>7400</v>
       </c>
       <c r="H17" s="3">
         <v>8000</v>
       </c>
       <c r="I17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K17" s="3">
         <v>8800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>13800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,49 +1239,55 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-8600</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-7400</v>
       </c>
       <c r="H18" s="3">
         <v>-8000</v>
       </c>
       <c r="I18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-8800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-13800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1100</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1306,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1250,49 +1317,55 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>4600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-17000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-13500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-3500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>8700</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1308,27 +1381,27 @@
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+      <c r="H21" s="3">
+        <v>-2400</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-26500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-6600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1414,14 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,58 +1470,70 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-8700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-8200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-2600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-25700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-27300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>7600</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1491,8 +1582,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1638,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-25700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-27300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>7600</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-8700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-25700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-27300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>7600</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1806,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1862,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1918,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1974,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1850,99 +1989,111 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-4600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>17000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>13500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>3500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-8700</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-8700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-25700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-27300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>7600</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2142,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-8700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-25700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-27300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>7600</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2285,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,47 +2307,49 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>100</v>
+      </c>
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>98100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>23200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,43 +2359,49 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>87100</v>
+      </c>
+      <c r="F42" s="3">
         <v>92700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>98800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>98700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>101700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>100500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>8100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>8100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2236,8 +2415,14 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2286,8 +2471,14 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,108 +2527,126 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F45" s="3">
         <v>2500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>91400</v>
+      </c>
+      <c r="F46" s="3">
         <v>96100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>101000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>106500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>111300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>116000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>111200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>32600</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3">
         <v>1500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>200</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
+      <c r="Q46" s="3">
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2469,14 +2678,14 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>275000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2486,43 +2695,49 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F48" s="3">
         <v>14700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>14600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>13300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>7600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7700</v>
       </c>
       <c r="I48" s="3">
         <v>7600</v>
       </c>
       <c r="J48" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="L48" s="3">
         <v>7500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2536,8 +2751,14 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2586,8 +2807,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2863,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,13 +2919,19 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
@@ -2704,25 +2943,25 @@
         <v>400</v>
       </c>
       <c r="H52" s="3">
+        <v>400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>400</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -2736,8 +2975,14 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,58 +3031,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>106700</v>
+      </c>
+      <c r="F54" s="3">
         <v>111200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>116100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>120100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>119400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>124000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>119000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>42200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3">
         <v>276500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>200</v>
       </c>
-      <c r="O54" s="3">
-        <v>0</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
+      <c r="Q54" s="3">
+        <v>0</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +3113,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,43 +3135,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -2926,8 +3187,14 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2962,40 +3229,46 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E59" s="3">
         <v>800</v>
       </c>
       <c r="F59" s="3">
+        <v>800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>800</v>
+      </c>
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3008,81 +3281,93 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
+      <c r="Q59" s="3">
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F60" s="3">
         <v>5400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4400</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
+      <c r="Q60" s="3">
+        <v>0</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -3126,47 +3411,53 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F62" s="3">
         <v>13200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>11500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>10200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>8800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>12900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>18800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>18600</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>23300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,8 +3467,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3523,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3579,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,58 +3635,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>18600</v>
+        <v>22900</v>
       </c>
       <c r="E66" s="3">
         <v>16900</v>
       </c>
       <c r="F66" s="3">
+        <v>18600</v>
+      </c>
+      <c r="G66" s="3">
+        <v>16900</v>
+      </c>
+      <c r="H66" s="3">
         <v>14500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>15700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>25100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>23000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3">
         <v>23400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3">
-        <v>0</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
+      <c r="Q66" s="3">
+        <v>0</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3717,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3769,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3825,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3520,14 +3855,14 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>54000</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3546,8 +3881,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,58 +3937,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-115800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-108400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-103500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-94800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-86600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-83200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-80600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-78600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-52800</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
         <v>5000</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +4049,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +4105,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,58 +4161,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>89900</v>
+      </c>
+      <c r="F76" s="3">
         <v>92600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>99200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>105700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>107300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>108300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>94000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-34800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3">
         <v>253000</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4273,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-8700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-25700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-27300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>7600</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>0</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4416,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4038,27 +4435,27 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3">
+        <v>1000</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J83" s="3">
+        <v>500</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>800</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -4071,8 +4468,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4524,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4580,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4636,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4692,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,8 +4748,14 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4338,41 +4771,47 @@
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="H89" s="3">
+        <v>-23900</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J89" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-11800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,26 +4830,28 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1700</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -4441,8 +4882,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4938,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,8 +4994,14 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4558,30 +5017,30 @@
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>-89900</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J94" s="3">
+        <v>-92700</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>19300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-275000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +5050,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +5076,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +5128,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +5184,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5240,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,8 +5296,14 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4828,30 +5319,30 @@
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>96900</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J100" s="3">
+        <v>96800</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>276600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4861,8 +5352,14 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4878,27 +5375,27 @@
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>-300</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
@@ -4911,8 +5408,14 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4928,37 +5431,43 @@
       <c r="G102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+      <c r="H102" s="3">
+        <v>-17200</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>7700</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>-4500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1200</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>DRTS</t>
   </si>
@@ -656,93 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -797,8 +801,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,8 +860,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,46 +944,47 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E12" s="3">
         <v>7500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11400</v>
-      </c>
-      <c r="M12" s="3">
-        <v>3000</v>
       </c>
       <c r="N12" s="3">
         <v>3000</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
+      <c r="O12" s="3">
+        <v>3000</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1060,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1082,11 +1102,11 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,55 +1200,56 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E17" s="3">
         <v>9900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
@@ -1230,8 +1257,11 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1239,46 +1269,46 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1100</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
+      <c r="R18" s="3">
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
@@ -1286,8 +1316,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1341,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1317,46 +1351,46 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F20" s="3">
         <v>4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-17000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-13500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8700</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1364,8 +1398,11 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1381,30 +1418,30 @@
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3">
-        <v>-2400</v>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-26500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-6600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1476,55 +1516,58 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7600</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
@@ -1532,8 +1575,11 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,55 +1693,58 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7600</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
@@ -1700,55 +1752,58 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7600</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
@@ -1756,8 +1811,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2047,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1989,46 +2059,46 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>17000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>13500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8700</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2036,55 +2106,58 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7600</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
@@ -2092,8 +2165,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,55 +2224,58 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7600</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
@@ -2204,69 +2283,75 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,50 +2395,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E41" s="3">
         <v>12700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>900</v>
       </c>
       <c r="G41" s="3">
         <v>900</v>
       </c>
       <c r="H41" s="3">
+        <v>900</v>
+      </c>
+      <c r="I41" s="3">
         <v>5800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>98100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,46 +2452,49 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>70300</v>
+      </c>
+      <c r="E42" s="3">
         <v>69100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>87100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>98800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>98700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>101700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>100500</v>
-      </c>
-      <c r="K42" s="3">
-        <v>8100</v>
       </c>
       <c r="L42" s="3">
         <v>8100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>8100</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2421,8 +2511,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,55 +2629,58 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
         <v>4000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2589,55 +2688,58 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E46" s="3">
         <v>85800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>91400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>96100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>101000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>106500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>111300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>116000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>111200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>32600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3">
         <v>1500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
+      <c r="R46" s="3">
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
@@ -2645,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2684,11 +2789,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>275000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,46 +2806,49 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E48" s="3">
         <v>21200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -2757,8 +2865,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,8 +3042,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2934,7 +3054,7 @@
         <v>500</v>
       </c>
       <c r="E52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
@@ -2949,22 +3069,22 @@
         <v>400</v>
       </c>
       <c r="J52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
       </c>
       <c r="L52" s="3">
+        <v>200</v>
+      </c>
+      <c r="M52" s="3">
         <v>2000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,55 +3160,58 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>102400</v>
+      </c>
+      <c r="E54" s="3">
         <v>107400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>111200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>116100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>120100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>124000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3">
         <v>276500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="Q54" s="3">
-        <v>0</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
+      <c r="R54" s="3">
+        <v>0</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,8 +3267,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3146,37 +3277,37 @@
         <v>6000</v>
       </c>
       <c r="E57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F57" s="3">
         <v>5400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3235,11 +3369,11 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3249,8 +3383,11 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3258,7 +3395,7 @@
         <v>1100</v>
       </c>
       <c r="E59" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="F59" s="3">
         <v>800</v>
@@ -3267,11 +3404,11 @@
         <v>800</v>
       </c>
       <c r="H59" s="3">
+        <v>800</v>
+      </c>
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3287,17 +3424,17 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
-        <v>100</v>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P59" s="3">
         <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3305,55 +3442,58 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4400</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3">
-        <v>100</v>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P60" s="3">
         <v>100</v>
       </c>
       <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
@@ -3361,17 +3501,20 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E61" s="3">
         <v>5600</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -3417,50 +3560,53 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E62" s="3">
         <v>10200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>23300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,55 +3796,58 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E66" s="3">
         <v>22900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3">
         <v>23400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3">
-        <v>0</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
+      <c r="R66" s="3">
+        <v>0</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3861,11 +4029,11 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>54000</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,55 +4114,58 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-123700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-115800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-108400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-103500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-94800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-86600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-83200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-80600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-78600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-52800</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3">
         <v>5000</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
       <c r="Q72" s="3">
         <v>0</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,55 +4350,58 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E76" s="3">
         <v>84500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>89900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>92600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>99200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>105700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>107300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>108300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>94000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-34800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3">
         <v>253000</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
       <c r="Q76" s="3">
         <v>0</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,116 +4468,122 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7600</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
         <v>0</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
@@ -4396,8 +4591,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4435,30 +4634,30 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
-        <v>1000</v>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,8 +4968,11 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4771,38 +4988,38 @@
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3">
-        <v>-23900</v>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-15300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-11800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,8 +5052,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,8 +5227,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5017,33 +5247,33 @@
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3">
-        <v>-89900</v>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-92700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>19300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>1300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-275000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,8 +5545,11 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5319,33 +5565,33 @@
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3">
-        <v>96900</v>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>96800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>276600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5375,30 +5624,30 @@
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
@@ -5414,8 +5663,11 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5431,43 +5683,46 @@
       <c r="G102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H102" s="3">
-        <v>-17200</v>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K102" s="3">
         <v>-11500</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>7700</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>-4500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1200</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>DRTS</t>
   </si>
@@ -656,97 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -804,8 +808,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -863,8 +870,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,49 +958,50 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E12" s="3">
         <v>6400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11400</v>
-      </c>
-      <c r="N12" s="3">
-        <v>3000</v>
       </c>
       <c r="O12" s="3">
         <v>3000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="P12" s="3">
+        <v>3000</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
@@ -1004,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,8 +1080,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1105,11 +1125,11 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1122,8 +1142,11 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,58 +1227,59 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E17" s="3">
         <v>8400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
         <v>0</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1260,8 +1287,11 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1269,49 +1299,49 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-9900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
+      <c r="S18" s="3">
+        <v>0</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
@@ -1319,8 +1349,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,8 +1375,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1351,49 +1385,49 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-17000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8700</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1401,8 +1435,11 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1427,24 +1464,24 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-26500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-6600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,8 +1497,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1519,58 +1559,61 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7600</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1578,8 +1621,11 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,58 +1745,61 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7600</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1755,58 +1807,61 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7600</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1814,8 +1869,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,8 +2117,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2059,49 +2129,49 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>17000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2109,58 +2179,61 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7600</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2168,8 +2241,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,58 +2303,61 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7600</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2286,72 +2365,78 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,53 +2482,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
         <v>7300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>900</v>
       </c>
       <c r="H41" s="3">
         <v>900</v>
       </c>
       <c r="I41" s="3">
+        <v>900</v>
+      </c>
+      <c r="J41" s="3">
         <v>5800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>98100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,49 +2542,52 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E42" s="3">
         <v>70300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>69100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>87100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>98800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>101700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100500</v>
-      </c>
-      <c r="L42" s="3">
-        <v>8100</v>
       </c>
       <c r="M42" s="3">
         <v>8100</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3">
+        <v>8100</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2514,8 +2604,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2573,8 +2666,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2632,58 +2728,61 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2691,58 +2790,61 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E46" s="3">
         <v>81200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>91400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>96100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>101000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>106500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>111300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>116000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>111200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3">
         <v>1500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
@@ -2750,8 +2852,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2792,11 +2897,11 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>275000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2809,49 +2914,52 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E48" s="3">
         <v>20800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -2868,8 +2976,11 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,19 +3162,22 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E52" s="3">
         <v>500</v>
       </c>
       <c r="F52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G52" s="3">
         <v>400</v>
@@ -3072,22 +3192,22 @@
         <v>400</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
+        <v>200</v>
+      </c>
+      <c r="N52" s="3">
         <v>2000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,58 +3286,61 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E54" s="3">
         <v>102400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>107400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>106700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>111200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>116100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>124000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>42200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3">
         <v>276500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3">
-        <v>0</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
+      <c r="S54" s="3">
+        <v>0</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,49 +3398,50 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6000</v>
+        <v>5400</v>
       </c>
       <c r="E57" s="3">
         <v>6000</v>
       </c>
       <c r="F57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G57" s="3">
         <v>5400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -3327,8 +3458,11 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3372,11 +3506,11 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3386,19 +3520,22 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
         <v>1100</v>
       </c>
       <c r="F59" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="G59" s="3">
         <v>800</v>
@@ -3407,11 +3544,11 @@
         <v>800</v>
       </c>
       <c r="I59" s="3">
+        <v>800</v>
+      </c>
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3427,17 +3564,17 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>100</v>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3445,58 +3582,61 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E60" s="3">
         <v>7000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3">
-        <v>100</v>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q60" s="3">
         <v>100</v>
       </c>
       <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S60" s="3">
+        <v>0</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -3504,20 +3644,23 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E61" s="3">
         <v>5500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5600</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -3563,53 +3706,56 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E62" s="3">
         <v>10900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>23300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,58 +3954,61 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E66" s="3">
         <v>23400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3">
         <v>23400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3">
-        <v>0</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
+      <c r="S66" s="3">
+        <v>0</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4032,11 +4200,11 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>54000</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,58 +4288,61 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-131100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-123700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-115800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-108400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-103500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-94800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-86600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-83200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-80600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-78600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-52800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>5000</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
         <v>0</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,58 +4536,61 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E76" s="3">
         <v>79100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>84500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>89900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>92600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>99200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>105700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>107300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>108300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>94000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-34800</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
         <v>253000</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
       <c r="R76" s="3">
         <v>0</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,122 +4660,128 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7600</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4594,8 +4789,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,50 +4815,51 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>400</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -4676,8 +4875,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,58 +5185,61 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-15300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-11800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5030,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,29 +5273,30 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -5112,8 +5333,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,53 +5457,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-92700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>19300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>1300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-275000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5289,8 +5519,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,53 +5791,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>96800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>276600</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5607,50 +5853,53 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
@@ -5666,63 +5915,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>-11500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>7700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>-4500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
   <si>
     <t>DRTS</t>
   </si>
@@ -656,124 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -811,8 +815,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,8 +880,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,52 +972,53 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E12" s="3">
         <v>6900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11400</v>
-      </c>
-      <c r="O12" s="3">
-        <v>3000</v>
       </c>
       <c r="P12" s="3">
         <v>3000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
+      <c r="Q12" s="3">
+        <v>3000</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,31 +1100,34 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1128,11 +1148,11 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1145,31 +1165,34 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,61 +1254,62 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E17" s="3">
         <v>9100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
       <c r="S17" s="3">
         <v>0</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1290,61 +1317,64 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-8300</v>
       </c>
       <c r="E18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1100</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
         <v>0</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
+      <c r="T18" s="3">
+        <v>0</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
@@ -1352,8 +1382,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,61 +1409,62 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2600</v>
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
-        <v>4000</v>
+        <v>-1800</v>
       </c>
       <c r="H20" s="3">
-        <v>-500</v>
+        <v>-1900</v>
       </c>
       <c r="I20" s="3">
-        <v>500</v>
-      </c>
-      <c r="J20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8700</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1438,53 +1472,56 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-8400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-26500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,31 +1537,34 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1562,61 +1602,64 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7600</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1624,8 +1667,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,61 +1797,64 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-27300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7600</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1810,61 +1862,64 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-27300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7600</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1872,8 +1927,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,61 +2187,64 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2600</v>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
-        <v>-4000</v>
+        <v>1800</v>
       </c>
       <c r="H32" s="3">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="I32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8700</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2182,61 +2252,64 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-27300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7600</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
         <v>0</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2317,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,61 +2382,64 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-27300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7600</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
         <v>0</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2368,75 +2447,81 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,56 +2569,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100</v>
-      </c>
-      <c r="H41" s="3">
-        <v>900</v>
       </c>
       <c r="I41" s="3">
         <v>900</v>
       </c>
       <c r="J41" s="3">
+        <v>900</v>
+      </c>
+      <c r="K41" s="3">
         <v>5800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>98100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,52 +2632,55 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E42" s="3">
         <v>68300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>70300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>69100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>87100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>92700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>98700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>101700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100500</v>
-      </c>
-      <c r="M42" s="3">
-        <v>8100</v>
       </c>
       <c r="N42" s="3">
         <v>8100</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>8100</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2607,31 +2697,34 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2669,31 +2762,34 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2731,61 +2827,64 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4200</v>
+        <v>3200</v>
       </c>
       <c r="E45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="M45" s="3">
         <v>4000</v>
       </c>
-      <c r="G45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>4000</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -2793,61 +2892,64 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E46" s="3">
         <v>75200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>81200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>85800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>91400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>96100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>101000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>111300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>116000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>111200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>32600</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3">
         <v>1500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
+      <c r="T46" s="3">
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
@@ -2855,31 +2957,34 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2900,11 +3005,11 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>275000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,52 +3022,55 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E48" s="3">
         <v>20400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -2979,8 +3087,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3174,13 +3294,13 @@
         <v>400</v>
       </c>
       <c r="E52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F52" s="3">
         <v>500</v>
       </c>
       <c r="G52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H52" s="3">
         <v>400</v>
@@ -3195,22 +3315,22 @@
         <v>400</v>
       </c>
       <c r="L52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
       </c>
       <c r="N52" s="3">
+        <v>200</v>
+      </c>
+      <c r="O52" s="3">
         <v>2000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,61 +3412,64 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>90700</v>
+      </c>
+      <c r="E54" s="3">
         <v>96000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>102400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>106700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>116100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>120100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>124000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>119000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3">
         <v>276500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3">
-        <v>0</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
+      <c r="T54" s="3">
+        <v>0</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,52 +3529,53 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5400</v>
+        <v>2500</v>
       </c>
       <c r="E57" s="3">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F57" s="3">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="G57" s="3">
-        <v>5400</v>
+        <v>2600</v>
       </c>
       <c r="H57" s="3">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="I57" s="3">
-        <v>4500</v>
+        <v>1800</v>
       </c>
       <c r="J57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K57" s="3">
         <v>3700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3461,31 +3592,34 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3509,11 +3643,11 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,35 +3657,38 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="E59" s="3">
-        <v>1100</v>
+        <v>3400</v>
       </c>
       <c r="F59" s="3">
-        <v>1100</v>
+        <v>3500</v>
       </c>
       <c r="G59" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="H59" s="3">
-        <v>800</v>
+        <v>3100</v>
       </c>
       <c r="I59" s="3">
-        <v>800</v>
+        <v>2800</v>
       </c>
       <c r="J59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3567,17 +3704,17 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
-        <v>100</v>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>0</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
@@ -3585,61 +3722,64 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4400</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3">
-        <v>100</v>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R60" s="3">
         <v>100</v>
       </c>
       <c r="S60" s="3">
-        <v>0</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T60" s="3">
+        <v>0</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
@@ -3647,32 +3787,35 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F61" s="3">
+        <v>11900</v>
+      </c>
+      <c r="G61" s="3">
+        <v>12200</v>
+      </c>
+      <c r="H61" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I61" s="3">
         <v>5400</v>
       </c>
-      <c r="E61" s="3">
-        <v>5500</v>
-      </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>5600</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3709,56 +3852,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I62" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K62" s="3">
         <v>10200</v>
       </c>
-      <c r="E62" s="3">
-        <v>10900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>10200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>10600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>13200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>11500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>10200</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>23300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,61 +4112,64 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E66" s="3">
         <v>22000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3">
         <v>23400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3">
-        <v>0</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
+      <c r="T66" s="3">
+        <v>0</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4203,11 +4371,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>54000</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,61 +4462,64 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-138000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-131100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-123700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-115800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-108400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-103500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-94800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-86600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-83200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-80600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-78600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-52800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
         <v>5000</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
       <c r="S72" s="3">
         <v>0</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,61 +4722,64 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E76" s="3">
         <v>74000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>79100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>84500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>89900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>92600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>99200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>105700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>107300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>108300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>94000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-34800</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3">
         <v>253000</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
       <c r="S76" s="3">
         <v>0</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,128 +4852,134 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-27300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7600</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
         <v>0</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4792,8 +4987,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,53 +5014,54 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>800</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,61 +5402,64 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-15300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-11800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,31 +5494,32 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,56 +5687,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>-92700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>19300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>1300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-275000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,31 +5779,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,56 +6037,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>96800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>276600</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,53 +6102,56 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
@@ -5918,8 +6167,11 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5944,40 +6196,43 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>-11500</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>7700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1200</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>DRTS</t>
   </si>
@@ -656,105 +656,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -779,8 +782,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -818,8 +821,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -883,8 +889,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,55 +985,56 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E12" s="3">
         <v>6200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11400</v>
-      </c>
-      <c r="P12" s="3">
-        <v>3000</v>
       </c>
       <c r="Q12" s="3">
         <v>3000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
+      <c r="R12" s="3">
+        <v>3000</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
@@ -1038,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1119,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1129,8 +1148,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1151,11 +1170,11 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1168,8 +1187,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1186,17 +1208,17 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1233,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,64 +1280,65 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E17" s="3">
         <v>8300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1320,64 +1346,67 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1100</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
+      <c r="U18" s="3">
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
@@ -1385,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,64 +1442,65 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8700</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1475,56 +1508,59 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-1500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-26500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-6600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,34 +1576,37 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>-200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1605,64 +1644,67 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-27300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7600</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1670,8 +1712,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1735,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,64 +1848,67 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-27300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7600</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1865,64 +1916,67 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-27300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7600</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -1930,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,64 +2256,67 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8700</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2255,64 +2324,67 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7600</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2320,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,64 +2460,67 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7600</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2450,78 +2528,84 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,59 +2655,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E41" s="3">
         <v>5500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
-      </c>
-      <c r="I41" s="3">
-        <v>900</v>
       </c>
       <c r="J41" s="3">
         <v>900</v>
       </c>
       <c r="K41" s="3">
+        <v>900</v>
+      </c>
+      <c r="L41" s="3">
         <v>5800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>98100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,55 +2721,58 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E42" s="3">
         <v>59700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>68300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>70300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>69100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>87100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>92700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>98800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>98700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>101700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>100500</v>
-      </c>
-      <c r="N42" s="3">
-        <v>8100</v>
       </c>
       <c r="O42" s="3">
         <v>8100</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>8100</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2700,13 +2789,16 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>300</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2714,20 +2806,20 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2765,8 +2857,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2791,8 +2886,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2830,64 +2925,67 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3100</v>
       </c>
       <c r="F45" s="3">
         <v>3100</v>
       </c>
       <c r="G45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>1900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -2895,64 +2993,67 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E46" s="3">
         <v>69800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>75200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>85800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>91400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>101000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>111300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>116000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>111200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>32600</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3">
         <v>1500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3">
-        <v>0</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
+      <c r="U46" s="3">
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
@@ -2960,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2986,8 +3090,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3008,11 +3112,11 @@
         <v>0</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>275000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3025,55 +3129,58 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E48" s="3">
         <v>20500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -3090,8 +3197,11 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3155,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3401,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3297,13 +3416,13 @@
         <v>400</v>
       </c>
       <c r="F52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G52" s="3">
         <v>500</v>
       </c>
       <c r="H52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
@@ -3318,22 +3437,22 @@
         <v>400</v>
       </c>
       <c r="M52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
       </c>
       <c r="O52" s="3">
+        <v>200</v>
+      </c>
+      <c r="P52" s="3">
         <v>2000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3350,8 +3469,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,64 +3537,67 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E54" s="3">
         <v>90700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>96000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>102400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>111200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>116100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>124000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3">
         <v>276500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="T54" s="3">
-        <v>0</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
+      <c r="U54" s="3">
+        <v>0</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
@@ -3480,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,55 +3659,56 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3595,8 +3725,11 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3607,13 +3740,13 @@
         <v>1000</v>
       </c>
       <c r="F58" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G58" s="3">
         <v>1100</v>
       </c>
       <c r="H58" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="I58" s="3">
         <v>800</v>
@@ -3622,7 +3755,7 @@
         <v>800</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3646,11 +3779,11 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,38 +3793,41 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3707,17 +3843,17 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
-        <v>100</v>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S59" s="3">
         <v>100</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
@@ -3725,64 +3861,67 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E60" s="3">
         <v>6300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4400</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3">
-        <v>100</v>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
       </c>
       <c r="T60" s="3">
-        <v>0</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="U60" s="3">
+        <v>0</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
@@ -3790,8 +3929,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3802,23 +3944,23 @@
         <v>11500</v>
       </c>
       <c r="F61" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G61" s="3">
         <v>11900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3855,59 +3997,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E62" s="3">
         <v>3400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3">
         <v>23300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,64 +4269,67 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E66" s="3">
         <v>21300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3">
         <v>23400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
+      <c r="U66" s="3">
+        <v>0</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
@@ -4180,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4374,11 +4541,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>54000</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4400,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,64 +4635,67 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-147500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-138000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-131100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-123700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-115800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-108400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-103500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-94800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-86600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-83200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-80600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-78600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-52800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3">
         <v>5000</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4530,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,64 +4907,67 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E76" s="3">
         <v>69400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>74000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>79100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>84500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>89900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>92600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>99200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>105700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>107300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>108300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>94000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-34800</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3">
         <v>253000</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
       <c r="T76" s="3">
         <v>0</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -4790,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,134 +5043,140 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7600</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -4990,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,8 +5212,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5035,36 +5233,36 @@
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
-        <v>200</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -5080,8 +5278,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,8 +5618,11 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5431,38 +5647,38 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-15300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-11800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -5470,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,8 +5714,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5521,8 +5741,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5560,8 +5780,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,8 +5916,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5716,33 +5945,33 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-92700</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>19300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>1300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-275000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5755,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5806,8 +6039,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5845,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,8 +6282,11 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6066,33 +6311,33 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>96800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>276600</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,8 +6350,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6125,36 +6373,36 @@
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -6170,8 +6418,11 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6199,40 +6450,43 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>-11500</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>7700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-4500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1200</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="92">
   <si>
     <t>DRTS</t>
   </si>
@@ -656,108 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -785,8 +789,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -824,8 +828,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -892,8 +899,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,58 +999,59 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E12" s="3">
         <v>7500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11400</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>3000</v>
       </c>
       <c r="R12" s="3">
         <v>3000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
+      <c r="S12" s="3">
+        <v>3000</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
@@ -1054,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,8 +1139,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1151,8 +1171,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1173,11 +1193,11 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,8 +1210,11 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1211,17 +1234,17 @@
         <v>300</v>
       </c>
       <c r="I15" s="3">
+        <v>300</v>
+      </c>
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,67 +1307,68 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E17" s="3">
         <v>10300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
         <v>0</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
@@ -1349,67 +1376,70 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1100</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
         <v>0</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
+      <c r="V18" s="3">
+        <v>0</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
@@ -1417,8 +1447,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,67 +1476,68 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>4600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8700</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1511,59 +1545,62 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-6600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,37 +1616,40 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1647,67 +1687,70 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7600</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+      <c r="V23" s="3">
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
@@ -1715,13 +1758,16 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,67 +1900,70 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7600</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+      <c r="V26" s="3">
+        <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
@@ -1919,67 +1971,70 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7600</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+      <c r="V27" s="3">
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
@@ -1987,8 +2042,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,67 +2326,70 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-4600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8700</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2327,67 +2397,70 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7600</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+      <c r="V33" s="3">
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
@@ -2395,8 +2468,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,67 +2539,70 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7600</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+      <c r="V35" s="3">
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
@@ -2531,81 +2610,87 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,62 +2742,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E41" s="3">
         <v>13700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
-      </c>
-      <c r="J41" s="3">
-        <v>900</v>
       </c>
       <c r="K41" s="3">
         <v>900</v>
       </c>
       <c r="L41" s="3">
+        <v>900</v>
+      </c>
+      <c r="M41" s="3">
         <v>5800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>98100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
         <v>1200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,58 +2811,61 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E42" s="3">
         <v>45900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>59700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>68300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>70300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>69100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>87100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>92700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>98800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>98700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>101700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>100500</v>
-      </c>
-      <c r="O42" s="3">
-        <v>8100</v>
       </c>
       <c r="P42" s="3">
         <v>8100</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3">
+        <v>8100</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2792,37 +2882,40 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2860,8 +2953,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2889,8 +2985,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2928,67 +3024,70 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3100</v>
       </c>
       <c r="G45" s="3">
         <v>3100</v>
       </c>
       <c r="H45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I45" s="3">
         <v>3200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1300</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
+      <c r="V45" s="3">
+        <v>0</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
@@ -2996,67 +3095,70 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E46" s="3">
         <v>64200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>69800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>81200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>85800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>91400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>96100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>101000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>111300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>116000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>111200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32600</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3">
         <v>1500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
+      <c r="V46" s="3">
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
@@ -3064,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3093,8 +3198,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3115,11 +3220,11 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>275000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3132,58 +3237,61 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E48" s="3">
         <v>21500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7500</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -3200,8 +3308,11 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,8 +3521,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3419,13 +3539,13 @@
         <v>400</v>
       </c>
       <c r="G52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H52" s="3">
         <v>500</v>
       </c>
       <c r="I52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J52" s="3">
         <v>400</v>
@@ -3440,22 +3560,22 @@
         <v>400</v>
       </c>
       <c r="N52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
       </c>
       <c r="P52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q52" s="3">
         <v>2000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,67 +3663,70 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>80900</v>
+      </c>
+      <c r="E54" s="3">
         <v>86200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>90700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>102400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>107400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>106700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>111200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>116100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>119400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>124000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>119000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>276500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>200</v>
       </c>
-      <c r="U54" s="3">
-        <v>0</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
+      <c r="V54" s="3">
+        <v>0</v>
       </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,58 +3790,59 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -3728,8 +3859,11 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3743,13 +3877,13 @@
         <v>1000</v>
       </c>
       <c r="G58" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H58" s="3">
         <v>1100</v>
       </c>
       <c r="I58" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="J58" s="3">
         <v>800</v>
@@ -3758,7 +3892,7 @@
         <v>800</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3782,11 +3916,11 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3796,41 +3930,44 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,17 +3983,17 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
-        <v>100</v>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T59" s="3">
         <v>100</v>
       </c>
       <c r="U59" s="3">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
@@ -3864,67 +4001,70 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E60" s="3">
         <v>8700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S60" s="3">
-        <v>100</v>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
       </c>
       <c r="U60" s="3">
-        <v>0</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
       </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
@@ -3932,13 +4072,16 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11500</v>
+        <v>11300</v>
       </c>
       <c r="E61" s="3">
         <v>11500</v>
@@ -3947,23 +4090,23 @@
         <v>11500</v>
       </c>
       <c r="G61" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H61" s="3">
         <v>11900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4000,62 +4143,65 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
         <v>3300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3">
         <v>23300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,67 +4427,70 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E66" s="3">
         <v>23500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3">
         <v>23400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>100</v>
       </c>
-      <c r="U66" s="3">
-        <v>0</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
+      <c r="V66" s="3">
+        <v>0</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4544,11 +4712,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>54000</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,67 +4809,70 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-156200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-147500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-138000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-131100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-123700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-115800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-108400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-103500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-94800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-86600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-83200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-80600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-78600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-52800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
         <v>5000</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
       <c r="U72" s="3">
         <v>0</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,67 +5093,70 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E76" s="3">
         <v>62700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>69400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>79100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>84500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>89900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>92600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>99200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>105700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>107300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>108300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>94000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3">
         <v>253000</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
       <c r="U76" s="3">
         <v>0</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,140 +5235,146 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7600</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+      <c r="V81" s="3">
+        <v>0</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
@@ -5187,8 +5382,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,8 +5411,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5236,36 +5435,36 @@
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
-        <v>200</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+        <v>200</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>800</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>400</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,8 +5835,11 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5650,38 +5867,38 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-15300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>-5400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,8 +5935,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5744,8 +5965,8 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,8 +6146,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5948,33 +6178,33 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-92700</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>19300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
         <v>1300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-275000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6042,8 +6276,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,8 +6528,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6314,33 +6560,33 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>96800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>276600</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,8 +6599,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6376,36 +6625,36 @@
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
@@ -6421,8 +6670,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6453,40 +6705,43 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>-11500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>7700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>-4500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1200</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="92">
   <si>
     <t>DRTS</t>
   </si>
@@ -656,112 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -792,8 +796,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -831,8 +835,11 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,8 +909,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,61 +1013,62 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="E12" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>7500</v>
       </c>
-      <c r="F12" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
         <v>6900</v>
       </c>
-      <c r="H12" s="3">
-        <v>6400</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>7500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11400</v>
-      </c>
-      <c r="R12" s="3">
-        <v>3000</v>
       </c>
       <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
+      <c r="T12" s="3">
+        <v>3000</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,8 +1159,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1174,8 +1194,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1196,11 +1216,11 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>900</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,8 +1233,11 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1222,32 +1245,32 @@
         <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,70 +1334,71 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9300</v>
-      </c>
-      <c r="E17" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
         <v>10300</v>
       </c>
-      <c r="F17" s="3">
-        <v>8300</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
         <v>9100</v>
       </c>
-      <c r="H17" s="3">
-        <v>8400</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
         <v>9900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1100</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
       <c r="V17" s="3">
         <v>0</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1379,70 +1406,73 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="E18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-10300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
         <v>-9100</v>
       </c>
-      <c r="H18" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>-9900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1100</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
+      <c r="W18" s="3">
+        <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
@@ -1450,8 +1480,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,70 +1510,71 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="E20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8700</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1548,62 +1582,65 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-8300</v>
+        <v>-10800</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-9700</v>
       </c>
-      <c r="F21" s="3">
-        <v>-8000</v>
-      </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-8800</v>
       </c>
-      <c r="H21" s="3">
-        <v>-8200</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-7900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-26500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-6600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,40 +1656,43 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1690,70 +1730,73 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="E23" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9500</v>
       </c>
-      <c r="F23" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3">
         <v>-7400</v>
       </c>
-      <c r="H23" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7600</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1761,28 +1804,31 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,70 +1952,73 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L26" s="3">
         <v>-8700</v>
       </c>
-      <c r="E26" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-27300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7600</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
         <v>0</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -1974,70 +2026,73 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L27" s="3">
         <v>-8700</v>
       </c>
-      <c r="E27" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-27300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7600</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2045,8 +2100,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,70 +2396,73 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>700</v>
-      </c>
-      <c r="E32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>17000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8700</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2400,70 +2470,73 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L33" s="3">
         <v>-8700</v>
       </c>
-      <c r="E33" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-27300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7600</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
         <v>0</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2471,8 +2544,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,70 +2618,73 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L35" s="3">
         <v>-8700</v>
       </c>
-      <c r="E35" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-27300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7600</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
         <v>0</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2613,84 +2692,90 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,65 +2829,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E41" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3">
         <v>13700</v>
       </c>
-      <c r="F41" s="3">
-        <v>5500</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3">
         <v>2800</v>
       </c>
-      <c r="H41" s="3">
-        <v>7300</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>12700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100</v>
-      </c>
-      <c r="K41" s="3">
-        <v>900</v>
       </c>
       <c r="L41" s="3">
         <v>900</v>
       </c>
       <c r="M41" s="3">
+        <v>900</v>
+      </c>
+      <c r="N41" s="3">
         <v>5800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>98100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>23200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3">
         <v>1200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,61 +2901,64 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>46600</v>
+        <v>68000</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>45900</v>
       </c>
-      <c r="F42" s="3">
-        <v>59700</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>68300</v>
       </c>
-      <c r="H42" s="3">
-        <v>70300</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>69100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>87100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>92700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>98800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>98700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>101700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>100500</v>
-      </c>
-      <c r="P42" s="3">
-        <v>8100</v>
       </c>
       <c r="Q42" s="3">
         <v>8100</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
+      <c r="R42" s="3">
+        <v>8100</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2885,40 +2975,43 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2988,8 +3084,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3027,70 +3123,73 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="E45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3100</v>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>3100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>3200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1300</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
+      <c r="W45" s="3">
+        <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
@@ -3098,70 +3197,73 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>56800</v>
-      </c>
-      <c r="E46" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3">
         <v>64200</v>
       </c>
-      <c r="F46" s="3">
-        <v>69800</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
         <v>75200</v>
       </c>
-      <c r="H46" s="3">
-        <v>81200</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>85800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>91400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>101000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>106500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>111300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>116000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>111200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32600</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3">
         <v>1500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
+      <c r="W46" s="3">
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3201,8 +3306,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3223,11 +3328,11 @@
         <v>0</v>
       </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
         <v>275000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3240,61 +3345,64 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>23700</v>
-      </c>
-      <c r="E48" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>21500</v>
       </c>
-      <c r="F48" s="3">
-        <v>20500</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
         <v>20400</v>
       </c>
-      <c r="H48" s="3">
-        <v>20800</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>21200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -3311,28 +3419,31 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
         <v>0</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,31 +3641,34 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>400</v>
+        <v>500</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>400</v>
       </c>
       <c r="K52" s="3">
         <v>400</v>
@@ -3563,22 +3683,22 @@
         <v>400</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
       </c>
       <c r="Q52" s="3">
+        <v>200</v>
+      </c>
+      <c r="R52" s="3">
         <v>2000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,70 +3789,73 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>80900</v>
-      </c>
-      <c r="E54" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3">
         <v>86200</v>
       </c>
-      <c r="F54" s="3">
-        <v>90700</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
         <v>96000</v>
       </c>
-      <c r="H54" s="3">
-        <v>102400</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>107400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>106700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>111200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>124000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>119000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3">
         <v>276500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>200</v>
       </c>
-      <c r="V54" s="3">
-        <v>0</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
+      <c r="W54" s="3">
+        <v>0</v>
       </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,61 +3921,62 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4400</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -3862,31 +3993,34 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1000</v>
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>1100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>800</v>
       </c>
       <c r="K58" s="3">
         <v>800</v>
@@ -3895,7 +4029,7 @@
         <v>800</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3919,11 +4053,11 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,44 +4067,47 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6200</v>
-      </c>
-      <c r="E59" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L59" s="3">
         <v>2800</v>
       </c>
-      <c r="G59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3986,17 +4123,17 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
-        <v>100</v>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U59" s="3">
         <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
@@ -4004,70 +4141,73 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9800</v>
-      </c>
-      <c r="E60" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3">
         <v>8700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
+        <v>7100</v>
+      </c>
+      <c r="K60" s="3">
+        <v>6200</v>
+      </c>
+      <c r="L60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="M60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="N60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O60" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q60" s="3">
         <v>6300</v>
       </c>
-      <c r="G60" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>7000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>6200</v>
-      </c>
-      <c r="K60" s="3">
-        <v>5400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>5300</v>
-      </c>
-      <c r="M60" s="3">
-        <v>4300</v>
-      </c>
-      <c r="N60" s="3">
-        <v>3400</v>
-      </c>
-      <c r="O60" s="3">
-        <v>2800</v>
-      </c>
-      <c r="P60" s="3">
-        <v>6300</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T60" s="3">
-        <v>100</v>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U60" s="3">
         <v>100</v>
       </c>
       <c r="V60" s="3">
-        <v>0</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W60" s="3">
+        <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
@@ -4075,41 +4215,44 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11300</v>
+        <v>12200</v>
       </c>
       <c r="E61" s="3">
-        <v>11500</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>11500</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>11500</v>
       </c>
-      <c r="H61" s="3">
-        <v>11900</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>12200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4146,65 +4289,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="E62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>3300</v>
       </c>
-      <c r="F62" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>4100</v>
       </c>
-      <c r="H62" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>3600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3">
         <v>23300</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,70 +4585,73 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>24600</v>
-      </c>
-      <c r="E66" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3">
         <v>23500</v>
       </c>
-      <c r="F66" s="3">
-        <v>21300</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3">
         <v>22000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
+        <v>22900</v>
+      </c>
+      <c r="K66" s="3">
+        <v>16900</v>
+      </c>
+      <c r="L66" s="3">
+        <v>18600</v>
+      </c>
+      <c r="M66" s="3">
+        <v>16900</v>
+      </c>
+      <c r="N66" s="3">
+        <v>14500</v>
+      </c>
+      <c r="O66" s="3">
+        <v>12100</v>
+      </c>
+      <c r="P66" s="3">
+        <v>15700</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>25100</v>
+      </c>
+      <c r="R66" s="3">
+        <v>23000</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3">
         <v>23400</v>
       </c>
-      <c r="I66" s="3">
-        <v>22900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>16900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>18600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>16900</v>
-      </c>
-      <c r="M66" s="3">
-        <v>14500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>12100</v>
-      </c>
-      <c r="O66" s="3">
-        <v>15700</v>
-      </c>
-      <c r="P66" s="3">
-        <v>25100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>23000</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3">
-        <v>23400</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>100</v>
       </c>
-      <c r="V66" s="3">
-        <v>0</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
+      <c r="W66" s="3">
+        <v>0</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4715,11 +4883,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>54000</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,70 +4983,73 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-156200</v>
-      </c>
-      <c r="E72" s="3">
+        <v>-166300</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>-147500</v>
       </c>
-      <c r="F72" s="3">
-        <v>-138000</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-131100</v>
       </c>
-      <c r="H72" s="3">
-        <v>-123700</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-115800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-108400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-103500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-94800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-86600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-83200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-80600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-78600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-52800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3">
         <v>5000</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
       <c r="V72" s="3">
         <v>0</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,70 +5279,73 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>56300</v>
-      </c>
-      <c r="E76" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3">
         <v>62700</v>
       </c>
-      <c r="F76" s="3">
-        <v>69400</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3">
         <v>74000</v>
       </c>
-      <c r="H76" s="3">
-        <v>79100</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3">
         <v>84500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>89900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>92600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>99200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>105700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>107300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>108300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>94000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-34800</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3">
         <v>253000</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
       <c r="V76" s="3">
         <v>0</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,146 +5427,152 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L81" s="3">
         <v>-8700</v>
       </c>
-      <c r="E81" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-27300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7600</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
         <v>0</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5385,8 +5580,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5438,36 +5637,36 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>200</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,8 +6052,11 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5870,38 +6087,38 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-15300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-11800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>-5400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,8 +6156,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5968,8 +6189,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,8 +6376,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6181,33 +6411,33 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>-92700</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>19300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>1300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-275000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6279,8 +6513,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,8 +6774,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6563,33 +6809,33 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>96800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>276600</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,8 +6848,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6628,36 +6877,36 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
@@ -6673,8 +6922,11 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6708,40 +6960,43 @@
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>-11500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>7700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-4500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1200</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DRTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="92">
   <si>
     <t>DRTS</t>
   </si>
@@ -656,118 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -801,8 +805,8 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -840,8 +844,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -914,8 +921,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,64 +1029,65 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E12" s="3">
         <v>7000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5400</v>
       </c>
       <c r="J12" s="3">
         <v>5400</v>
       </c>
       <c r="K12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L12" s="3">
         <v>6700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>3000</v>
       </c>
       <c r="T12" s="3">
         <v>3000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
+      <c r="U12" s="3">
+        <v>3000</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,8 +1181,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1199,8 +1219,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1221,11 +1241,11 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>900</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1238,8 +1258,11 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,7 +1282,7 @@
         <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
@@ -1268,14 +1291,14 @@
         <v>200</v>
       </c>
       <c r="L15" s="3">
+        <v>200</v>
+      </c>
+      <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,73 +1363,74 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E17" s="3">
         <v>9600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>8000</v>
       </c>
       <c r="J17" s="3">
         <v>8000</v>
       </c>
       <c r="K17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L17" s="3">
         <v>8900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1100</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+      <c r="X17" s="3">
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
@@ -1411,73 +1438,76 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-8000</v>
       </c>
       <c r="J18" s="3">
         <v>-8000</v>
       </c>
       <c r="K18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="L18" s="3">
         <v>-8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
+      <c r="X18" s="3">
+        <v>0</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
@@ -1485,8 +1515,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,73 +1546,74 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E20" s="3">
         <v>1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-17000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-13500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8700</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1587,65 +1621,68 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-26500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-6600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1661,43 +1698,46 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>-6200</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1735,73 +1775,76 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-7400</v>
       </c>
       <c r="G23" s="3">
         <v>-7400</v>
       </c>
       <c r="H23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7600</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+      <c r="X23" s="3">
+        <v>0</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1809,17 +1852,20 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1883,8 +1929,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,73 +2006,76 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-7400</v>
       </c>
       <c r="G26" s="3">
         <v>-7400</v>
       </c>
       <c r="H26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I26" s="3">
         <v>-8700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-25700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-27300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7600</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>0</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2031,73 +2083,76 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-7400</v>
       </c>
       <c r="G27" s="3">
         <v>-7400</v>
       </c>
       <c r="H27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I27" s="3">
         <v>-8700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-25700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-27300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7600</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
@@ -2105,8 +2160,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,73 +2468,76 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>-4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>17000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>13500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8700</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2475,73 +2545,76 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-7400</v>
       </c>
       <c r="G33" s="3">
         <v>-7400</v>
       </c>
       <c r="H33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I33" s="3">
         <v>-8700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-25700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-27300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7600</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
@@ -2549,8 +2622,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,73 +2699,76 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-7400</v>
       </c>
       <c r="G35" s="3">
         <v>-7400</v>
       </c>
       <c r="H35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I35" s="3">
         <v>-8700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-25700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-27300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7600</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
@@ -2697,87 +2776,93 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,68 +2918,69 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E41" s="3">
         <v>11700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100</v>
-      </c>
-      <c r="L41" s="3">
-        <v>900</v>
       </c>
       <c r="M41" s="3">
         <v>900</v>
       </c>
       <c r="N41" s="3">
+        <v>900</v>
+      </c>
+      <c r="O41" s="3">
         <v>5800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>98100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3">
         <v>1200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,64 +2993,67 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E42" s="3">
         <v>68000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>45900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>68300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>69100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>92700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>100500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>87100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>92700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>98800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>98700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>101700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100500</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>8100</v>
       </c>
       <c r="R42" s="3">
         <v>8100</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
+      <c r="S42" s="3">
+        <v>8100</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2980,31 +3070,34 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
+        <v>300</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -3015,8 +3108,8 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3054,8 +3147,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3089,8 +3185,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -3128,73 +3224,76 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E45" s="3">
         <v>3600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>2900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
+      <c r="X45" s="3">
+        <v>0</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
@@ -3202,73 +3301,76 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E46" s="3">
         <v>85800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>64200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>85800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>96100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>106500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>116000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>91400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>96100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>101000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>106500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>111300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>116000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>111200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32600</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3">
         <v>1500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
+      <c r="X46" s="3">
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
@@ -3276,8 +3378,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3311,8 +3416,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3333,11 +3438,11 @@
         <v>0</v>
       </c>
       <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
         <v>275000</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,64 +3455,67 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E48" s="3">
         <v>24700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7500</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3424,8 +3532,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,8 +3763,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3655,25 +3775,25 @@
         <v>500</v>
       </c>
       <c r="E52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
       </c>
       <c r="G52" s="3">
+        <v>400</v>
+      </c>
+      <c r="H52" s="3">
         <v>500</v>
-      </c>
-      <c r="H52" s="3">
-        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
       </c>
       <c r="J52" s="3">
+        <v>400</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
@@ -3688,22 +3808,22 @@
         <v>400</v>
       </c>
       <c r="P52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
       </c>
       <c r="R52" s="3">
+        <v>200</v>
+      </c>
+      <c r="S52" s="3">
         <v>2000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,73 +3917,76 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105700</v>
+      </c>
+      <c r="E54" s="3">
         <v>111000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>86200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>124000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>106700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>111200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>116100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>120100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>119400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>124000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>119000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3">
         <v>276500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>200</v>
       </c>
-      <c r="W54" s="3">
-        <v>0</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
+      <c r="X54" s="3">
+        <v>0</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
@@ -3868,8 +3994,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,64 +4054,65 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -3998,8 +4129,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4007,25 +4141,25 @@
         <v>1100</v>
       </c>
       <c r="E58" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F58" s="3">
         <v>1000</v>
       </c>
       <c r="G58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>800</v>
@@ -4034,7 +4168,7 @@
         <v>800</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4058,11 +4192,11 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4072,47 +4206,50 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>4700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M59" s="3">
         <v>2800</v>
       </c>
-      <c r="I59" s="3">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4128,17 +4265,17 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
-        <v>100</v>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V59" s="3">
         <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
@@ -4146,73 +4283,76 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E60" s="3">
         <v>8200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U60" s="3">
-        <v>100</v>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V60" s="3">
         <v>100</v>
       </c>
       <c r="W60" s="3">
-        <v>0</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="X60" s="3">
+        <v>0</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
@@ -4220,44 +4360,47 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E61" s="3">
         <v>12200</v>
-      </c>
-      <c r="E61" s="3">
-        <v>11500</v>
       </c>
       <c r="F61" s="3">
         <v>11500</v>
       </c>
       <c r="G61" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H61" s="3">
         <v>12200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>5200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4294,68 +4437,71 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E62" s="3">
         <v>3800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
         <v>23300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,73 +4745,76 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E66" s="3">
         <v>24300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3">
         <v>23400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3">
-        <v>0</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
+      <c r="X66" s="3">
+        <v>0</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
@@ -4664,8 +4822,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4888,11 +5056,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>54000</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,73 +5159,76 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-190100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-166300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-147500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-131100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-115800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-103500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-86600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-80600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-108400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-103500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-94800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-86600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-83200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-80600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-78600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-52800</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
         <v>5000</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
       <c r="W72" s="3">
         <v>0</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
@@ -5062,8 +5236,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,73 +5467,76 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E76" s="3">
         <v>86600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>62700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>84500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>92600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>105700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>108300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>89900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>92600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>99200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>105700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>107300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>108300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>94000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-34800</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3">
         <v>253000</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
       <c r="W76" s="3">
         <v>0</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
+      <c r="X76" s="3">
+        <v>0</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
@@ -5358,8 +5544,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,152 +5621,158 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-7400</v>
       </c>
       <c r="G81" s="3">
         <v>-7400</v>
       </c>
       <c r="H81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I81" s="3">
         <v>-8700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-25700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-27300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7600</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
@@ -5585,8 +5780,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5624,54 +5823,54 @@
       <c r="E83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
-        <v>200</v>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>800</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,8 +6271,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6080,50 +6297,50 @@
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-8700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>-11800</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>-5400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
@@ -6131,8 +6348,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6379,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6182,20 +6403,20 @@
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6608,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6404,45 +6634,45 @@
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-92400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-92700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
         <v>19300</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
         <v>1300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-275000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6455,8 +6685,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6518,8 +6752,8 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7022,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6802,45 +7048,45 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>14800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>96800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>276600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6853,8 +7099,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6864,54 +7113,54 @@
       <c r="E101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
@@ -6927,8 +7176,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6951,11 +7203,11 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-86500</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -6965,40 +7217,43 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>7700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
         <v>-4500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1200</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
+      <c r="X102" s="3">
+        <v>0</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
